--- a/data/externalStats/File1/RPT_RPT6659694529226EG_externalStats.xlsx
+++ b/data/externalStats/File1/RPT_RPT6659694529226EG_externalStats.xlsx
@@ -2101,7 +2101,7 @@
         </is>
       </c>
       <c r="AH25" s="119" t="n">
-        <v>28321838.53519511</v>
+        <v>18109457.88932022</v>
       </c>
       <c r="AI25" s="46" t="n">
         <v>37842.21210599999</v>
@@ -2178,7 +2178,7 @@
         </is>
       </c>
       <c r="AH26" s="122" t="n">
-        <v>12577936.89957107</v>
+        <v>9757022.106748115</v>
       </c>
       <c r="AI26" s="56" t="n">
         <v>1010.22492</v>
@@ -2255,7 +2255,7 @@
         </is>
       </c>
       <c r="AH27" s="122" t="n">
-        <v>11053644.90468685</v>
+        <v>7759533.542697988</v>
       </c>
       <c r="AI27" s="56" t="n">
         <v>14824.49351</v>
@@ -2332,7 +2332,7 @@
         </is>
       </c>
       <c r="AH28" s="122" t="n">
-        <v>9782432.197343033</v>
+        <v>7588478.775918763</v>
       </c>
       <c r="AI28" s="56" t="n">
         <v>486.126805</v>
@@ -2409,7 +2409,7 @@
         </is>
       </c>
       <c r="AH29" s="122" t="n">
-        <v>8455132.003897959</v>
+        <v>6558858.621744173</v>
       </c>
       <c r="AI29" s="56" t="n">
         <v>653.7931</v>
@@ -2486,7 +2486,7 @@
         </is>
       </c>
       <c r="AH30" s="122" t="n">
-        <v>7349724.884596497</v>
+        <v>5701366.50788654</v>
       </c>
       <c r="AI30" s="56" t="n">
         <v>563.805105</v>
@@ -2549,7 +2549,7 @@
         </is>
       </c>
       <c r="AH31" s="122" t="n">
-        <v>6188704.374589607</v>
+        <v>4800733.687657373</v>
       </c>
       <c r="AI31" s="56" t="n">
         <v>3352.283312</v>
@@ -2620,7 +2620,7 @@
         </is>
       </c>
       <c r="AH32" s="122" t="n">
-        <v>5634318.81464013</v>
+        <v>4370682.860778647</v>
       </c>
       <c r="AI32" s="56" t="n">
         <v>752.332995</v>
@@ -2697,7 +2697,7 @@
         </is>
       </c>
       <c r="AH33" s="122" t="n">
-        <v>3525876.647080136</v>
+        <v>2475125.476378681</v>
       </c>
       <c r="AI33" s="56" t="n">
         <v>12388.239665</v>
@@ -2774,7 +2774,7 @@
         </is>
       </c>
       <c r="AH34" s="122" t="n">
-        <v>3362331.971915809</v>
+        <v>2608245.504978427</v>
       </c>
       <c r="AI34" s="56" t="n">
         <v>478.74527</v>
@@ -2851,7 +2851,7 @@
         </is>
       </c>
       <c r="AH35" s="122" t="n">
-        <v>2841021.190740636</v>
+        <v>1994364.701884032</v>
       </c>
       <c r="AI35" s="56" t="n">
         <v>2964.457539</v>
@@ -2928,7 +2928,7 @@
         </is>
       </c>
       <c r="AH36" s="122" t="n">
-        <v>2790844.477037583</v>
+        <v>2164928.276900498</v>
       </c>
       <c r="AI36" s="56" t="n">
         <v>340.6051150000001</v>
@@ -3005,7 +3005,7 @@
         </is>
       </c>
       <c r="AH37" s="122" t="n">
-        <v>2727048.747105429</v>
+        <v>1914357.337168013</v>
       </c>
       <c r="AI37" s="56" t="n">
         <v>6267.339120000001</v>
@@ -3082,7 +3082,7 @@
         </is>
       </c>
       <c r="AH38" s="122" t="n">
-        <v>1948582.403595467</v>
+        <v>1511564.395695904</v>
       </c>
       <c r="AI38" s="56" t="n">
         <v>379.6218000000001</v>
@@ -3145,7 +3145,7 @@
         </is>
       </c>
       <c r="AH39" s="122" t="n">
-        <v>1941215.895906649</v>
+        <v>1362711.57503163</v>
       </c>
       <c r="AI39" s="56" t="n">
         <v>2057.340789</v>
@@ -3212,7 +3212,7 @@
         </is>
       </c>
       <c r="AH40" s="122" t="n">
-        <v>1886765.755512452</v>
+        <v>1463611.666506141</v>
       </c>
       <c r="AI40" s="56" t="n">
         <v>432.34705</v>
@@ -3289,7 +3289,7 @@
         </is>
       </c>
       <c r="AH41" s="122" t="n">
-        <v>1789458.473543813</v>
+        <v>1256179.583156397</v>
       </c>
       <c r="AI41" s="56" t="n">
         <v>2313.124427</v>
@@ -3366,7 +3366,7 @@
         </is>
       </c>
       <c r="AH42" s="122" t="n">
-        <v>1681735.878437424</v>
+        <v>1180559.541329281</v>
       </c>
       <c r="AI42" s="56" t="n">
         <v>292.326032</v>
@@ -3443,7 +3443,7 @@
         </is>
       </c>
       <c r="AH43" s="122" t="n">
-        <v>1553571.067329031</v>
+        <v>1090589.295372904</v>
       </c>
       <c r="AI43" s="56" t="n">
         <v>3118.807607</v>
@@ -3520,7 +3520,7 @@
         </is>
       </c>
       <c r="AH44" s="125" t="n">
-        <v>1286115.311408092</v>
+        <v>902838.3836011493</v>
       </c>
       <c r="AI44" s="84" t="n">
         <v>2198.851002</v>
@@ -3694,7 +3694,7 @@
         </is>
       </c>
       <c r="AG49" s="119" t="n">
-        <v>56807208.64813554</v>
+        <v>44066780.98547408</v>
       </c>
       <c r="AH49" s="46" t="n">
         <v>6193.368443736876</v>
@@ -3710,7 +3710,7 @@
         </is>
       </c>
       <c r="AG50" s="122" t="n">
-        <v>42381230.48405989</v>
+        <v>27978991.81752676</v>
       </c>
       <c r="AH50" s="56" t="n">
         <v>56332.8797098342</v>
@@ -3756,7 +3756,7 @@
         </is>
       </c>
       <c r="AG51" s="122" t="n">
-        <v>7830360.385887323</v>
+        <v>6049423.402662692</v>
       </c>
       <c r="AH51" s="56" t="n">
         <v>4113.677334999999</v>
@@ -3877,7 +3877,7 @@
         </is>
       </c>
       <c r="AG52" s="122" t="n">
-        <v>7638705.398830292</v>
+        <v>5362284.683116573</v>
       </c>
       <c r="AH52" s="56" t="n">
         <v>11001.53729257186</v>
@@ -3958,7 +3958,7 @@
         </is>
       </c>
       <c r="AG53" s="122" t="n">
-        <v>4432201.733347513</v>
+        <v>3111355.422981945</v>
       </c>
       <c r="AH53" s="56" t="n">
         <v>22887.512402</v>
@@ -4039,7 +4039,7 @@
         </is>
       </c>
       <c r="AG54" s="122" t="n">
-        <v>3806675.586098987</v>
+        <v>2672243.151576201</v>
       </c>
       <c r="AH54" s="56" t="n">
         <v>13940.70394875373</v>
@@ -4120,7 +4120,7 @@
         </is>
       </c>
       <c r="AG55" s="122" t="n">
-        <v>3425914.538456521</v>
+        <v>2404953.208176464</v>
       </c>
       <c r="AH55" s="56" t="n">
         <v>8674.453556973891</v>
@@ -4201,7 +4201,7 @@
         </is>
       </c>
       <c r="AG56" s="122" t="n">
-        <v>2409033.856227719</v>
+        <v>1725765.356886142</v>
       </c>
       <c r="AH56" s="56" t="n">
         <v>674.7266581255167</v>
@@ -4282,7 +4282,7 @@
         </is>
       </c>
       <c r="AG57" s="122" t="n">
-        <v>1515157.938424984</v>
+        <v>1175346.133349708</v>
       </c>
       <c r="AH57" s="56" t="n">
         <v>412.827386</v>
@@ -4363,7 +4363,7 @@
         </is>
       </c>
       <c r="AG58" s="122" t="n">
-        <v>1436232.948787194</v>
+        <v>1114122.033179747</v>
       </c>
       <c r="AH58" s="56" t="n">
         <v>1312.036472</v>
@@ -4444,7 +4444,7 @@
         </is>
       </c>
       <c r="AG59" s="122" t="n">
-        <v>1378098.727412943</v>
+        <v>967409.6999421467</v>
       </c>
       <c r="AH59" s="56" t="n">
         <v>4568.302288</v>
@@ -4525,7 +4525,7 @@
         </is>
       </c>
       <c r="AG60" s="122" t="n">
-        <v>1287332.948799934</v>
+        <v>998616.556950173</v>
       </c>
       <c r="AH60" s="56" t="n">
         <v>361.6921428652741</v>
@@ -4606,7 +4606,7 @@
         </is>
       </c>
       <c r="AG61" s="122" t="n">
-        <v>1205806.390981769</v>
+        <v>935374.3548887171</v>
       </c>
       <c r="AH61" s="56" t="n">
         <v>3116.524085999999</v>
@@ -4687,7 +4687,7 @@
         </is>
       </c>
       <c r="AG62" s="122" t="n">
-        <v>1151527.348521048</v>
+        <v>893243.5068292584</v>
       </c>
       <c r="AH62" s="56" t="n">
         <v>1318.0278084067</v>
@@ -4715,49 +4715,49 @@
         <v>0</v>
       </c>
       <c r="J63" s="130" t="n">
-        <v>1964.875071784408</v>
+        <v>1964.875071784398</v>
       </c>
       <c r="K63" s="131" t="n">
-        <v>347.8756485030455</v>
+        <v>347.8756485030435</v>
       </c>
       <c r="L63" s="131" t="n">
-        <v>130.6682137649018</v>
+        <v>130.668213764901</v>
       </c>
       <c r="M63" s="131" t="n">
-        <v>663.932716975576</v>
+        <v>663.9327169755762</v>
       </c>
       <c r="N63" s="132" t="n">
-        <v>3107.351651027931</v>
+        <v>3107.351651027918</v>
       </c>
       <c r="P63" s="130" t="n">
-        <v>2163.155319482375</v>
+        <v>2163.155319482363</v>
       </c>
       <c r="Q63" s="131" t="n">
-        <v>372.0859813343212</v>
+        <v>372.0859813343191</v>
       </c>
       <c r="R63" s="131" t="n">
-        <v>143.0165673943964</v>
+        <v>143.0165673943955</v>
       </c>
       <c r="S63" s="131" t="n">
-        <v>753.6182474419385</v>
+        <v>753.6182474419381</v>
       </c>
       <c r="T63" s="132" t="n">
-        <v>3431.876115653031</v>
+        <v>3431.876115653015</v>
       </c>
       <c r="V63" s="130" t="n">
-        <v>2378.866087308556</v>
+        <v>2378.866087308544</v>
       </c>
       <c r="W63" s="131" t="n">
-        <v>407.7078036315904</v>
+        <v>407.7078036315881</v>
       </c>
       <c r="X63" s="131" t="n">
-        <v>157.7761316534636</v>
+        <v>157.7761316534625</v>
       </c>
       <c r="Y63" s="131" t="n">
-        <v>854.1693686244979</v>
+        <v>854.1693686244977</v>
       </c>
       <c r="Z63" s="132" t="n">
-        <v>3798.519391218108</v>
+        <v>3798.519391218092</v>
       </c>
       <c r="AE63" s="121" t="n">
         <v>15</v>
@@ -4768,7 +4768,7 @@
         </is>
       </c>
       <c r="AG63" s="122" t="n">
-        <v>989013.90751893</v>
+        <v>694276.5626869352</v>
       </c>
       <c r="AH63" s="56" t="n">
         <v>2747.2099006045</v>
@@ -4849,7 +4849,7 @@
         </is>
       </c>
       <c r="AG64" s="122" t="n">
-        <v>969673.8223267702</v>
+        <v>680700.0419047659</v>
       </c>
       <c r="AH64" s="56" t="n">
         <v>5248.563888</v>
@@ -4935,7 +4935,7 @@
         </is>
       </c>
       <c r="AG65" s="122" t="n">
-        <v>846389.1662489668</v>
+        <v>594155.6095130505</v>
       </c>
       <c r="AH65" s="56" t="n">
         <v>2651.990643</v>
@@ -5017,7 +5017,7 @@
         </is>
       </c>
       <c r="AG66" s="122" t="n">
-        <v>673094.1243892565</v>
+        <v>472504.4526603898</v>
       </c>
       <c r="AH66" s="56" t="n">
         <v>520.349192</v>
@@ -5098,7 +5098,7 @@
         </is>
       </c>
       <c r="AG67" s="122" t="n">
-        <v>439421.1727234393</v>
+        <v>308468.6868920012</v>
       </c>
       <c r="AH67" s="56" t="n">
         <v>6706.464778411767</v>
@@ -5126,49 +5126,49 @@
         <v>0</v>
       </c>
       <c r="J68" s="142" t="n">
-        <v>1964.875071784408</v>
+        <v>1964.875071784398</v>
       </c>
       <c r="K68" s="143" t="n">
-        <v>347.8756485030455</v>
+        <v>347.8756485030435</v>
       </c>
       <c r="L68" s="143" t="n">
-        <v>130.6682137649018</v>
+        <v>130.668213764901</v>
       </c>
       <c r="M68" s="143" t="n">
-        <v>663.932716975576</v>
+        <v>663.9327169755762</v>
       </c>
       <c r="N68" s="144" t="n">
-        <v>3107.351651027931</v>
+        <v>3107.351651027918</v>
       </c>
       <c r="P68" s="142" t="n">
-        <v>2163.155319482375</v>
+        <v>2163.155319482363</v>
       </c>
       <c r="Q68" s="143" t="n">
-        <v>372.0859813343212</v>
+        <v>372.0859813343191</v>
       </c>
       <c r="R68" s="143" t="n">
-        <v>143.0165673943964</v>
+        <v>143.0165673943955</v>
       </c>
       <c r="S68" s="143" t="n">
-        <v>753.6182474419385</v>
+        <v>753.6182474419381</v>
       </c>
       <c r="T68" s="144" t="n">
-        <v>3431.876115653031</v>
+        <v>3431.876115653015</v>
       </c>
       <c r="V68" s="142" t="n">
-        <v>2378.866087308556</v>
+        <v>2378.866087308544</v>
       </c>
       <c r="W68" s="143" t="n">
-        <v>407.7078036315904</v>
+        <v>407.7078036315881</v>
       </c>
       <c r="X68" s="143" t="n">
-        <v>157.7761316534636</v>
+        <v>157.7761316534625</v>
       </c>
       <c r="Y68" s="143" t="n">
-        <v>854.1693686244979</v>
+        <v>854.1693686244977</v>
       </c>
       <c r="Z68" s="144" t="n">
-        <v>3798.519391218108</v>
+        <v>3798.519391218092</v>
       </c>
       <c r="AE68" s="124" t="n">
         <v>20</v>
@@ -5179,7 +5179,7 @@
         </is>
       </c>
       <c r="AG68" s="125" t="n">
-        <v>374474.1478201752</v>
+        <v>262876.6109224144</v>
       </c>
       <c r="AH68" s="84" t="n">
         <v>3384.39584879385</v>
@@ -7211,49 +7211,49 @@
         <v>0</v>
       </c>
       <c r="J99" s="130" t="n">
-        <v>1964.875071784408</v>
+        <v>1964.875071784398</v>
       </c>
       <c r="K99" s="131" t="n">
-        <v>347.8756485030455</v>
+        <v>347.8756485030435</v>
       </c>
       <c r="L99" s="131" t="n">
-        <v>130.6682137649018</v>
+        <v>130.668213764901</v>
       </c>
       <c r="M99" s="131" t="n">
-        <v>663.932716975576</v>
+        <v>663.9327169755762</v>
       </c>
       <c r="N99" s="132" t="n">
-        <v>3107.351651027931</v>
+        <v>3107.351651027918</v>
       </c>
       <c r="P99" s="130" t="n">
-        <v>2163.155319482375</v>
+        <v>2163.155319482363</v>
       </c>
       <c r="Q99" s="131" t="n">
-        <v>372.0859813343212</v>
+        <v>372.0859813343191</v>
       </c>
       <c r="R99" s="131" t="n">
-        <v>143.0165673943964</v>
+        <v>143.0165673943955</v>
       </c>
       <c r="S99" s="131" t="n">
-        <v>753.6182474419385</v>
+        <v>753.6182474419381</v>
       </c>
       <c r="T99" s="132" t="n">
-        <v>3431.876115653031</v>
+        <v>3431.876115653015</v>
       </c>
       <c r="V99" s="130" t="n">
-        <v>2378.866087308556</v>
+        <v>2378.866087308544</v>
       </c>
       <c r="W99" s="131" t="n">
-        <v>407.7078036315904</v>
+        <v>407.7078036315881</v>
       </c>
       <c r="X99" s="131" t="n">
-        <v>157.7761316534636</v>
+        <v>157.7761316534625</v>
       </c>
       <c r="Y99" s="131" t="n">
-        <v>854.1693686244979</v>
+        <v>854.1693686244977</v>
       </c>
       <c r="Z99" s="132" t="n">
-        <v>3798.519391218108</v>
+        <v>3798.519391218092</v>
       </c>
     </row>
     <row r="100">
@@ -7550,49 +7550,49 @@
         <v>0</v>
       </c>
       <c r="J104" s="142" t="n">
-        <v>1964.875071784408</v>
+        <v>1964.875071784398</v>
       </c>
       <c r="K104" s="143" t="n">
-        <v>347.8756485030455</v>
+        <v>347.8756485030435</v>
       </c>
       <c r="L104" s="143" t="n">
-        <v>130.6682137649018</v>
+        <v>130.668213764901</v>
       </c>
       <c r="M104" s="143" t="n">
-        <v>663.932716975576</v>
+        <v>663.9327169755762</v>
       </c>
       <c r="N104" s="144" t="n">
-        <v>3107.351651027931</v>
+        <v>3107.351651027918</v>
       </c>
       <c r="P104" s="142" t="n">
-        <v>2163.155319482375</v>
+        <v>2163.155319482363</v>
       </c>
       <c r="Q104" s="143" t="n">
-        <v>372.0859813343212</v>
+        <v>372.0859813343191</v>
       </c>
       <c r="R104" s="143" t="n">
-        <v>143.0165673943964</v>
+        <v>143.0165673943955</v>
       </c>
       <c r="S104" s="143" t="n">
-        <v>753.6182474419385</v>
+        <v>753.6182474419381</v>
       </c>
       <c r="T104" s="144" t="n">
-        <v>3431.876115653031</v>
+        <v>3431.876115653015</v>
       </c>
       <c r="V104" s="142" t="n">
-        <v>2378.866087308556</v>
+        <v>2378.866087308544</v>
       </c>
       <c r="W104" s="143" t="n">
-        <v>407.7078036315904</v>
+        <v>407.7078036315881</v>
       </c>
       <c r="X104" s="143" t="n">
-        <v>157.7761316534636</v>
+        <v>157.7761316534625</v>
       </c>
       <c r="Y104" s="143" t="n">
-        <v>854.1693686244979</v>
+        <v>854.1693686244977</v>
       </c>
       <c r="Z104" s="144" t="n">
-        <v>3798.519391218108</v>
+        <v>3798.519391218092</v>
       </c>
     </row>
     <row r="105" ht="30.3" customHeight="1" thickBot="1"/>
@@ -7603,7 +7603,7 @@
         </is>
       </c>
       <c r="H106" s="111" t="n">
-        <v>-1576682</v>
+        <v>0</v>
       </c>
     </row>
     <row r="107" ht="15" customHeight="1" thickBot="1"/>
@@ -7614,7 +7614,7 @@
         </is>
       </c>
       <c r="H108" s="113" t="n">
-        <v>0</v>
+        <v>1576682</v>
       </c>
     </row>
     <row r="109"/>
@@ -8625,7 +8625,7 @@
         </is>
       </c>
       <c r="AH25" s="119" t="n">
-        <v>36479078.07321157</v>
+        <v>31735416.09662873</v>
       </c>
       <c r="AI25" s="46" t="n">
         <v>47681.18725356001</v>
@@ -8702,7 +8702,7 @@
         </is>
       </c>
       <c r="AH26" s="122" t="n">
-        <v>16000083.88751766</v>
+        <v>13696166.13392816</v>
       </c>
       <c r="AI26" s="56" t="n">
         <v>1224.14004681</v>
@@ -8779,7 +8779,7 @@
         </is>
       </c>
       <c r="AH27" s="122" t="n">
-        <v>11038368.61023807</v>
+        <v>9602962.557628859</v>
       </c>
       <c r="AI27" s="56" t="n">
         <v>14231.5137696</v>
@@ -8856,7 +8856,7 @@
         </is>
       </c>
       <c r="AH28" s="122" t="n">
-        <v>10108103.37976938</v>
+        <v>8652596.083964711</v>
       </c>
       <c r="AI28" s="56" t="n">
         <v>495.2368213257</v>
@@ -8933,7 +8933,7 @@
         </is>
       </c>
       <c r="AH29" s="122" t="n">
-        <v>9576725.592281304</v>
+        <v>8197733.565212943</v>
       </c>
       <c r="AI29" s="56" t="n">
         <v>683.1908359837499</v>
@@ -9010,7 +9010,7 @@
         </is>
       </c>
       <c r="AH30" s="122" t="n">
-        <v>8736615.461358383</v>
+        <v>7478594.340393441</v>
       </c>
       <c r="AI30" s="56" t="n">
         <v>666.0451826940001</v>
@@ -9073,7 +9073,7 @@
         </is>
       </c>
       <c r="AH31" s="122" t="n">
-        <v>8104574.014232034</v>
+        <v>6937563.13554306</v>
       </c>
       <c r="AI31" s="56" t="n">
         <v>4224.614475448639</v>
@@ -9144,7 +9144,7 @@
         </is>
       </c>
       <c r="AH32" s="122" t="n">
-        <v>7261041.493413352</v>
+        <v>6215494.324796574</v>
       </c>
       <c r="AI32" s="56" t="n">
         <v>911.6395066912501</v>
@@ -9221,7 +9221,7 @@
         </is>
       </c>
       <c r="AH33" s="122" t="n">
-        <v>4000601.555590695</v>
+        <v>3480371.810622171</v>
       </c>
       <c r="AI33" s="56" t="n">
         <v>13968.60739906405</v>
@@ -9298,7 +9298,7 @@
         </is>
       </c>
       <c r="AH34" s="122" t="n">
-        <v>3598308.439208843</v>
+        <v>3080173.237277076</v>
       </c>
       <c r="AI34" s="56" t="n">
         <v>487.7169563598</v>
@@ -9375,7 +9375,7 @@
         </is>
       </c>
       <c r="AH35" s="122" t="n">
-        <v>3207480.443483342</v>
+        <v>2790386.486507542</v>
       </c>
       <c r="AI35" s="56" t="n">
         <v>3203.748551548079</v>
@@ -9452,7 +9452,7 @@
         </is>
       </c>
       <c r="AH36" s="122" t="n">
-        <v>3009386.504461526</v>
+        <v>2576052.589228084</v>
       </c>
       <c r="AI36" s="56" t="n">
         <v>346.9880548551</v>
@@ -9529,7 +9529,7 @@
         </is>
       </c>
       <c r="AH37" s="122" t="n">
-        <v>2903419.373107377</v>
+        <v>2525864.873110362</v>
       </c>
       <c r="AI37" s="56" t="n">
         <v>6422.6437833936</v>
@@ -9606,7 +9606,7 @@
         </is>
       </c>
       <c r="AH38" s="122" t="n">
-        <v>2230525.508568964</v>
+        <v>1940472.700173931</v>
       </c>
       <c r="AI38" s="56" t="n">
         <v>2223.40933748808</v>
@@ -9669,7 +9669,7 @@
         </is>
       </c>
       <c r="AH39" s="122" t="n">
-        <v>2065048.249427686</v>
+        <v>1767693.475707591</v>
       </c>
       <c r="AI39" s="56" t="n">
         <v>386.7359125319999</v>
@@ -9736,7 +9736,7 @@
         </is>
       </c>
       <c r="AH40" s="122" t="n">
-        <v>1934184.360180434</v>
+        <v>1682667.126475263</v>
       </c>
       <c r="AI40" s="56" t="n">
         <v>318.39566753376</v>
@@ -9813,7 +9813,7 @@
         </is>
       </c>
       <c r="AH41" s="122" t="n">
-        <v>1791403.502580468</v>
+        <v>1558453.188900565</v>
       </c>
       <c r="AI41" s="56" t="n">
         <v>5750.841219200001</v>
@@ -9890,7 +9890,7 @@
         </is>
       </c>
       <c r="AH42" s="122" t="n">
-        <v>1751697.250307624</v>
+        <v>1523910.253495579</v>
       </c>
       <c r="AI42" s="56" t="n">
         <v>2220.59944992</v>
@@ -9967,7 +9967,7 @@
         </is>
       </c>
       <c r="AH43" s="122" t="n">
-        <v>1677255.769387772</v>
+        <v>1459148.984937764</v>
       </c>
       <c r="AI43" s="56" t="n">
         <v>3262.52226153056</v>
@@ -10044,7 +10044,7 @@
         </is>
       </c>
       <c r="AH44" s="125" t="n">
-        <v>1469210.384293677</v>
+        <v>1278157.380662738</v>
       </c>
       <c r="AI44" s="84" t="n">
         <v>2376.34225488144</v>
@@ -10218,7 +10218,7 @@
         </is>
       </c>
       <c r="AG49" s="119" t="n">
-        <v>63825929.65793302</v>
+        <v>54635372.06385777</v>
       </c>
       <c r="AH49" s="46" t="n">
         <v>6596.229291898628</v>
@@ -10234,7 +10234,7 @@
         </is>
       </c>
       <c r="AG50" s="122" t="n">
-        <v>50483834.20567334</v>
+        <v>43919023.43186639</v>
       </c>
       <c r="AH50" s="56" t="n">
         <v>65432.22815324085</v>
@@ -10280,7 +10280,7 @@
         </is>
       </c>
       <c r="AG51" s="122" t="n">
-        <v>9888326.187878195</v>
+        <v>8469505.215599423</v>
       </c>
       <c r="AH51" s="56" t="n">
         <v>5005.6285081715</v>
@@ -10401,7 +10401,7 @@
         </is>
       </c>
       <c r="AG52" s="122" t="n">
-        <v>8695847.306631757</v>
+        <v>7565057.758171883</v>
       </c>
       <c r="AH52" s="56" t="n">
         <v>11889.58138282826</v>
@@ -10482,7 +10482,7 @@
         </is>
       </c>
       <c r="AG53" s="122" t="n">
-        <v>4677651.474507733</v>
+        <v>4069379.593436714</v>
       </c>
       <c r="AH53" s="56" t="n">
         <v>23454.66495932156</v>
@@ -10563,7 +10563,7 @@
         </is>
       </c>
       <c r="AG54" s="122" t="n">
-        <v>4319207.333582764</v>
+        <v>3757546.768692</v>
       </c>
       <c r="AH54" s="56" t="n">
         <v>15397.00541642564</v>
@@ -10644,7 +10644,7 @@
         </is>
       </c>
       <c r="AG55" s="122" t="n">
-        <v>3675991.790008769</v>
+        <v>3197973.610780149</v>
       </c>
       <c r="AH55" s="56" t="n">
         <v>9074.172376879247</v>
@@ -10725,7 +10725,7 @@
         </is>
       </c>
       <c r="AG56" s="122" t="n">
-        <v>2761791.590981672</v>
+        <v>2395089.70579707</v>
       </c>
       <c r="AH56" s="56" t="n">
         <v>714.9946921332024</v>
@@ -10806,7 +10806,7 @@
         </is>
       </c>
       <c r="AG57" s="122" t="n">
-        <v>1945845.153215983</v>
+        <v>1692811.574705483</v>
       </c>
       <c r="AH57" s="56" t="n">
         <v>6395.6232032</v>
@@ -10887,7 +10887,7 @@
         </is>
       </c>
       <c r="AG58" s="122" t="n">
-        <v>1711383.037607484</v>
+        <v>1464953.969406672</v>
       </c>
       <c r="AH58" s="56" t="n">
         <v>1526.26578714816</v>
@@ -10968,7 +10968,7 @@
         </is>
       </c>
       <c r="AG59" s="122" t="n">
-        <v>1611604.857738647</v>
+        <v>1379543.259210915</v>
       </c>
       <c r="AH59" s="56" t="n">
         <v>420.2046113878201</v>
@@ -11049,7 +11049,7 @@
         </is>
       </c>
       <c r="AG60" s="122" t="n">
-        <v>1447765.841267964</v>
+        <v>1239296.095222452</v>
       </c>
       <c r="AH60" s="56" t="n">
         <v>3677.49842148</v>
@@ -11130,7 +11130,7 @@
         </is>
       </c>
       <c r="AG61" s="122" t="n">
-        <v>1270553.669559002</v>
+        <v>1087601.431510492</v>
       </c>
       <c r="AH61" s="56" t="n">
         <v>340.076453072452</v>
@@ -11211,7 +11211,7 @@
         </is>
       </c>
       <c r="AG62" s="122" t="n">
-        <v>1186145.123178522</v>
+        <v>1015352.460948401</v>
       </c>
       <c r="AH62" s="56" t="n">
         <v>1331.685307452391</v>
@@ -11239,49 +11239,49 @@
         <v>0</v>
       </c>
       <c r="J63" s="130" t="n">
-        <v>1964.875071784408</v>
+        <v>1964.875071784398</v>
       </c>
       <c r="K63" s="131" t="n">
-        <v>347.8756485030455</v>
+        <v>347.8756485030435</v>
       </c>
       <c r="L63" s="131" t="n">
-        <v>130.6682137649018</v>
+        <v>130.668213764901</v>
       </c>
       <c r="M63" s="131" t="n">
-        <v>663.932716975576</v>
+        <v>663.9327169755762</v>
       </c>
       <c r="N63" s="132" t="n">
-        <v>3107.351651027931</v>
+        <v>3107.351651027918</v>
       </c>
       <c r="P63" s="130" t="n">
-        <v>2163.155319482375</v>
+        <v>2163.155319482363</v>
       </c>
       <c r="Q63" s="131" t="n">
-        <v>372.0859813343212</v>
+        <v>372.0859813343191</v>
       </c>
       <c r="R63" s="131" t="n">
-        <v>143.0165673943964</v>
+        <v>143.0165673943955</v>
       </c>
       <c r="S63" s="131" t="n">
-        <v>753.6182474419385</v>
+        <v>753.6182474419381</v>
       </c>
       <c r="T63" s="132" t="n">
-        <v>3431.876115653031</v>
+        <v>3431.876115653015</v>
       </c>
       <c r="V63" s="130" t="n">
-        <v>2378.866087308556</v>
+        <v>2378.866087308544</v>
       </c>
       <c r="W63" s="131" t="n">
-        <v>407.7078036315904</v>
+        <v>407.7078036315881</v>
       </c>
       <c r="X63" s="131" t="n">
-        <v>157.7761316534636</v>
+        <v>157.7761316534625</v>
       </c>
       <c r="Y63" s="131" t="n">
-        <v>854.1693686244979</v>
+        <v>854.1693686244977</v>
       </c>
       <c r="Z63" s="132" t="n">
-        <v>3798.519391218108</v>
+        <v>3798.519391218092</v>
       </c>
       <c r="AE63" s="121" t="n">
         <v>15</v>
@@ -11292,7 +11292,7 @@
         </is>
       </c>
       <c r="AG63" s="122" t="n">
-        <v>1106322.558871141</v>
+        <v>962458.7187318605</v>
       </c>
       <c r="AH63" s="56" t="n">
         <v>2947.497985345487</v>
@@ -11373,7 +11373,7 @@
         </is>
       </c>
       <c r="AG64" s="122" t="n">
-        <v>975487.09410515</v>
+        <v>848636.8204313753</v>
       </c>
       <c r="AH64" s="56" t="n">
         <v>5010.38405876256</v>
@@ -11459,7 +11459,7 @@
         </is>
       </c>
       <c r="AG65" s="122" t="n">
-        <v>812687.5827582901</v>
+        <v>707007.4124032579</v>
       </c>
       <c r="AH65" s="56" t="n">
         <v>2531.64330762066</v>
@@ -11541,7 +11541,7 @@
         </is>
       </c>
       <c r="AG66" s="122" t="n">
-        <v>723702.4021857894</v>
+        <v>629593.6760628171</v>
       </c>
       <c r="AH66" s="56" t="n">
         <v>537.67613711196</v>
@@ -11622,7 +11622,7 @@
         </is>
       </c>
       <c r="AG67" s="122" t="n">
-        <v>419466.3110586537</v>
+        <v>364919.8012419043</v>
       </c>
       <c r="AH67" s="56" t="n">
         <v>3573.328306204676</v>
@@ -11650,49 +11650,49 @@
         <v>0</v>
       </c>
       <c r="J68" s="142" t="n">
-        <v>1964.875071784408</v>
+        <v>1964.875071784398</v>
       </c>
       <c r="K68" s="143" t="n">
-        <v>347.8756485030455</v>
+        <v>347.8756485030435</v>
       </c>
       <c r="L68" s="143" t="n">
-        <v>130.6682137649018</v>
+        <v>130.668213764901</v>
       </c>
       <c r="M68" s="143" t="n">
-        <v>663.932716975576</v>
+        <v>663.9327169755762</v>
       </c>
       <c r="N68" s="144" t="n">
-        <v>3107.351651027931</v>
+        <v>3107.351651027918</v>
       </c>
       <c r="P68" s="142" t="n">
-        <v>2163.155319482375</v>
+        <v>2163.155319482363</v>
       </c>
       <c r="Q68" s="143" t="n">
-        <v>372.0859813343212</v>
+        <v>372.0859813343191</v>
       </c>
       <c r="R68" s="143" t="n">
-        <v>143.0165673943964</v>
+        <v>143.0165673943955</v>
       </c>
       <c r="S68" s="143" t="n">
-        <v>753.6182474419385</v>
+        <v>753.6182474419381</v>
       </c>
       <c r="T68" s="144" t="n">
-        <v>3431.876115653031</v>
+        <v>3431.876115653015</v>
       </c>
       <c r="V68" s="142" t="n">
-        <v>2378.866087308556</v>
+        <v>2378.866087308544</v>
       </c>
       <c r="W68" s="143" t="n">
-        <v>407.7078036315904</v>
+        <v>407.7078036315881</v>
       </c>
       <c r="X68" s="143" t="n">
-        <v>157.7761316534636</v>
+        <v>157.7761316534625</v>
       </c>
       <c r="Y68" s="143" t="n">
-        <v>854.1693686244979</v>
+        <v>854.1693686244977</v>
       </c>
       <c r="Z68" s="144" t="n">
-        <v>3798.519391218108</v>
+        <v>3798.519391218092</v>
       </c>
       <c r="AE68" s="124" t="n">
         <v>20</v>
@@ -11703,7 +11703,7 @@
         </is>
       </c>
       <c r="AG68" s="125" t="n">
-        <v>374807.2770586585</v>
+        <v>326068.1333456119</v>
       </c>
       <c r="AH68" s="84" t="n">
         <v>387.23436488</v>
@@ -13735,49 +13735,49 @@
         <v>0</v>
       </c>
       <c r="J99" s="130" t="n">
-        <v>1964.875071784408</v>
+        <v>1964.875071784398</v>
       </c>
       <c r="K99" s="131" t="n">
-        <v>347.8756485030455</v>
+        <v>347.8756485030435</v>
       </c>
       <c r="L99" s="131" t="n">
-        <v>130.6682137649018</v>
+        <v>130.668213764901</v>
       </c>
       <c r="M99" s="131" t="n">
-        <v>663.932716975576</v>
+        <v>663.9327169755762</v>
       </c>
       <c r="N99" s="132" t="n">
-        <v>3107.351651027931</v>
+        <v>3107.351651027918</v>
       </c>
       <c r="P99" s="130" t="n">
-        <v>2163.155319482375</v>
+        <v>2163.155319482363</v>
       </c>
       <c r="Q99" s="131" t="n">
-        <v>372.0859813343212</v>
+        <v>372.0859813343191</v>
       </c>
       <c r="R99" s="131" t="n">
-        <v>143.0165673943964</v>
+        <v>143.0165673943955</v>
       </c>
       <c r="S99" s="131" t="n">
-        <v>753.6182474419385</v>
+        <v>753.6182474419381</v>
       </c>
       <c r="T99" s="132" t="n">
-        <v>3431.876115653031</v>
+        <v>3431.876115653015</v>
       </c>
       <c r="V99" s="130" t="n">
-        <v>2378.866087308556</v>
+        <v>2378.866087308544</v>
       </c>
       <c r="W99" s="131" t="n">
-        <v>407.7078036315904</v>
+        <v>407.7078036315881</v>
       </c>
       <c r="X99" s="131" t="n">
-        <v>157.7761316534636</v>
+        <v>157.7761316534625</v>
       </c>
       <c r="Y99" s="131" t="n">
-        <v>854.1693686244979</v>
+        <v>854.1693686244977</v>
       </c>
       <c r="Z99" s="132" t="n">
-        <v>3798.519391218108</v>
+        <v>3798.519391218092</v>
       </c>
     </row>
     <row r="100">
@@ -14074,49 +14074,49 @@
         <v>0</v>
       </c>
       <c r="J104" s="142" t="n">
-        <v>1964.875071784408</v>
+        <v>1964.875071784398</v>
       </c>
       <c r="K104" s="143" t="n">
-        <v>347.8756485030455</v>
+        <v>347.8756485030435</v>
       </c>
       <c r="L104" s="143" t="n">
-        <v>130.6682137649018</v>
+        <v>130.668213764901</v>
       </c>
       <c r="M104" s="143" t="n">
-        <v>663.932716975576</v>
+        <v>663.9327169755762</v>
       </c>
       <c r="N104" s="144" t="n">
-        <v>3107.351651027931</v>
+        <v>3107.351651027918</v>
       </c>
       <c r="P104" s="142" t="n">
-        <v>2163.155319482375</v>
+        <v>2163.155319482363</v>
       </c>
       <c r="Q104" s="143" t="n">
-        <v>372.0859813343212</v>
+        <v>372.0859813343191</v>
       </c>
       <c r="R104" s="143" t="n">
-        <v>143.0165673943964</v>
+        <v>143.0165673943955</v>
       </c>
       <c r="S104" s="143" t="n">
-        <v>753.6182474419385</v>
+        <v>753.6182474419381</v>
       </c>
       <c r="T104" s="144" t="n">
-        <v>3431.876115653031</v>
+        <v>3431.876115653015</v>
       </c>
       <c r="V104" s="142" t="n">
-        <v>2378.866087308556</v>
+        <v>2378.866087308544</v>
       </c>
       <c r="W104" s="143" t="n">
-        <v>407.7078036315904</v>
+        <v>407.7078036315881</v>
       </c>
       <c r="X104" s="143" t="n">
-        <v>157.7761316534636</v>
+        <v>157.7761316534625</v>
       </c>
       <c r="Y104" s="143" t="n">
-        <v>854.1693686244979</v>
+        <v>854.1693686244977</v>
       </c>
       <c r="Z104" s="144" t="n">
-        <v>3798.519391218108</v>
+        <v>3798.519391218092</v>
       </c>
     </row>
     <row r="105" ht="30.3" customHeight="1" thickBot="1"/>
@@ -14127,7 +14127,7 @@
         </is>
       </c>
       <c r="H106" s="111" t="n">
-        <v>-1576682</v>
+        <v>0</v>
       </c>
     </row>
     <row r="107" ht="15" customHeight="1" thickBot="1"/>
@@ -14138,7 +14138,7 @@
         </is>
       </c>
       <c r="H108" s="113" t="n">
-        <v>0</v>
+        <v>1576682</v>
       </c>
     </row>
     <row r="109"/>
@@ -15149,7 +15149,7 @@
         </is>
       </c>
       <c r="AH25" s="119" t="n">
-        <v>45226774.22397625</v>
+        <v>39319209.66723216</v>
       </c>
       <c r="AI25" s="46" t="n">
         <v>57217.42470427202</v>
@@ -15226,7 +15226,7 @@
         </is>
       </c>
       <c r="AH26" s="122" t="n">
-        <v>20010985.9187456</v>
+        <v>17118955.31976605</v>
       </c>
       <c r="AI26" s="56" t="n">
         <v>1458.856659385349</v>
@@ -15303,7 +15303,7 @@
         </is>
       </c>
       <c r="AH27" s="122" t="n">
-        <v>12268638.86353412</v>
+        <v>10495548.86460844</v>
       </c>
       <c r="AI27" s="56" t="n">
         <v>814.1858468752741</v>
@@ -15380,7 +15380,7 @@
         </is>
       </c>
       <c r="AH28" s="122" t="n">
-        <v>11115532.63897398</v>
+        <v>9663611.121818261</v>
       </c>
       <c r="AI28" s="56" t="n">
         <v>13662.253218816</v>
@@ -15457,7 +15457,7 @@
         </is>
       </c>
       <c r="AH29" s="122" t="n">
-        <v>10521414.80268533</v>
+        <v>9000837.37199421</v>
       </c>
       <c r="AI29" s="56" t="n">
         <v>508.3853589318973</v>
@@ -15534,7 +15534,7 @@
         </is>
       </c>
       <c r="AH30" s="122" t="n">
-        <v>10338954.44928697</v>
+        <v>8844746.580159249</v>
       </c>
       <c r="AI30" s="56" t="n">
         <v>5158.465505246562</v>
@@ -15597,7 +15597,7 @@
         </is>
       </c>
       <c r="AH31" s="122" t="n">
-        <v>9200041.749933772</v>
+        <v>7870431.986540079</v>
       </c>
       <c r="AI31" s="56" t="n">
         <v>1086.43726570423</v>
@@ -15668,7 +15668,7 @@
         </is>
       </c>
       <c r="AH32" s="122" t="n">
-        <v>9093847.954155255</v>
+        <v>7779585.545862422</v>
       </c>
       <c r="AI32" s="56" t="n">
         <v>683.7286822945256</v>
@@ -15745,7 +15745,7 @@
         </is>
       </c>
       <c r="AH33" s="122" t="n">
-        <v>4604846.28437676</v>
+        <v>4003356.853268552</v>
       </c>
       <c r="AI33" s="56" t="n">
         <v>15719.43265046274</v>
@@ -15822,7 +15822,7 @@
         </is>
       </c>
       <c r="AH34" s="122" t="n">
-        <v>3909046.280218133</v>
+        <v>3344102.528764696</v>
       </c>
       <c r="AI34" s="56" t="n">
         <v>500.6658415511526</v>
@@ -15899,7 +15899,7 @@
         </is>
       </c>
       <c r="AH35" s="122" t="n">
-        <v>3642243.861988861</v>
+        <v>3166490.481048035</v>
       </c>
       <c r="AI35" s="56" t="n">
         <v>3453.51278862677</v>
@@ -15976,7 +15976,7 @@
         </is>
       </c>
       <c r="AH36" s="122" t="n">
-        <v>3268902.308421254</v>
+        <v>2796473.536574826</v>
       </c>
       <c r="AI36" s="56" t="n">
         <v>356.2005877115029</v>
@@ -16053,7 +16053,7 @@
         </is>
       </c>
       <c r="AH37" s="122" t="n">
-        <v>3112786.495935575</v>
+        <v>2706191.343138849</v>
       </c>
       <c r="AI37" s="56" t="n">
         <v>6581.796896346093</v>
@@ -16130,7 +16130,7 @@
         </is>
       </c>
       <c r="AH38" s="122" t="n">
-        <v>2569349.041505356</v>
+        <v>2233738.209383379</v>
       </c>
       <c r="AI38" s="56" t="n">
         <v>2396.746329438651</v>
@@ -16193,7 +16193,7 @@
         </is>
       </c>
       <c r="AH39" s="122" t="n">
-        <v>2565277.661491391</v>
+        <v>2230198.636925452</v>
       </c>
       <c r="AI39" s="56" t="n">
         <v>8051.177706879999</v>
@@ -16260,7 +16260,7 @@
         </is>
       </c>
       <c r="AH40" s="122" t="n">
-        <v>2275993.38056727</v>
+        <v>1978700.945784349</v>
       </c>
       <c r="AI40" s="56" t="n">
         <v>349.0667221872872</v>
@@ -16337,7 +16337,7 @@
         </is>
       </c>
       <c r="AH41" s="122" t="n">
-        <v>2204566.834283146</v>
+        <v>1885958.10765015</v>
       </c>
       <c r="AI41" s="56" t="n">
         <v>397.0037510097247</v>
@@ -16414,7 +16414,7 @@
         </is>
       </c>
       <c r="AH42" s="122" t="n">
-        <v>1840597.694286198</v>
+        <v>1600177.060965291</v>
       </c>
       <c r="AI42" s="56" t="n">
         <v>3412.859287341888</v>
@@ -16491,7 +16491,7 @@
         </is>
       </c>
       <c r="AH43" s="122" t="n">
-        <v>1737800.745879648</v>
+        <v>1510807.548394438</v>
       </c>
       <c r="AI43" s="56" t="n">
         <v>2131.775471923199</v>
@@ -16568,7 +16568,7 @@
         </is>
       </c>
       <c r="AH44" s="125" t="n">
-        <v>1706579.149043358</v>
+        <v>1459940.670626835</v>
       </c>
       <c r="AI44" s="84" t="n">
         <v>3947.949967310399</v>
@@ -16742,7 +16742,7 @@
         </is>
       </c>
       <c r="AG49" s="119" t="n">
-        <v>73915427.95898302</v>
+        <v>63233011.79707871</v>
       </c>
       <c r="AH49" s="46" t="n">
         <v>7144.845202353837</v>
@@ -16758,7 +16758,7 @@
         </is>
       </c>
       <c r="AG50" s="122" t="n">
-        <v>59303348.32311717</v>
+        <v>51557088.17829858</v>
       </c>
       <c r="AH50" s="56" t="n">
         <v>74258.42396796562</v>
@@ -16804,7 +16804,7 @@
         </is>
       </c>
       <c r="AG51" s="122" t="n">
-        <v>12251018.2339162</v>
+        <v>10485568.10018733</v>
       </c>
       <c r="AH51" s="56" t="n">
         <v>5932.289759414654</v>
@@ -16925,7 +16925,7 @@
         </is>
       </c>
       <c r="AG52" s="122" t="n">
-        <v>9959895.441076633</v>
+        <v>8658924.361308822</v>
       </c>
       <c r="AH52" s="56" t="n">
         <v>12816.49314743355</v>
@@ -17006,7 +17006,7 @@
         </is>
       </c>
       <c r="AG53" s="122" t="n">
-        <v>4974297.504515781</v>
+        <v>4324550.001259193</v>
       </c>
       <c r="AH53" s="56" t="n">
         <v>24035.87155701355</v>
@@ -17087,7 +17087,7 @@
         </is>
       </c>
       <c r="AG54" s="122" t="n">
-        <v>4971573.790873248</v>
+        <v>4322182.061700783</v>
       </c>
       <c r="AH54" s="56" t="n">
         <v>17288.0539711389</v>
@@ -17168,7 +17168,7 @@
         </is>
       </c>
       <c r="AG55" s="122" t="n">
-        <v>4007987.619888676</v>
+        <v>3484460.439067294</v>
       </c>
       <c r="AH55" s="56" t="n">
         <v>9492.310240005841</v>
@@ -17249,7 +17249,7 @@
         </is>
       </c>
       <c r="AG56" s="122" t="n">
-        <v>3237558.697110137</v>
+        <v>2805798.160532758</v>
       </c>
       <c r="AH56" s="56" t="n">
         <v>761.1241252540833</v>
@@ -17330,7 +17330,7 @@
         </is>
       </c>
       <c r="AG57" s="122" t="n">
-        <v>2792867.850268204</v>
+        <v>2428060.777311677</v>
       </c>
       <c r="AH57" s="56" t="n">
         <v>8953.872484479998</v>
@@ -17411,7 +17411,7 @@
         </is>
       </c>
       <c r="AG58" s="122" t="n">
-        <v>2001771.712862789</v>
+        <v>1712471.372076092</v>
       </c>
       <c r="AH58" s="56" t="n">
         <v>1714.561197308629</v>
@@ -17492,7 +17492,7 @@
         </is>
       </c>
       <c r="AG59" s="122" t="n">
-        <v>1768806.807101554</v>
+        <v>1513175.05409387</v>
       </c>
       <c r="AH59" s="56" t="n">
         <v>4339.448137346399</v>
@@ -17573,7 +17573,7 @@
         </is>
       </c>
       <c r="AG60" s="122" t="n">
-        <v>1709553.141100614</v>
+        <v>1462484.854974185</v>
       </c>
       <c r="AH60" s="56" t="n">
         <v>430.9954658082593</v>
@@ -17654,7 +17654,7 @@
         </is>
       </c>
       <c r="AG61" s="122" t="n">
-        <v>1329608.399260626</v>
+        <v>1137456.276208713</v>
       </c>
       <c r="AH61" s="56" t="n">
         <v>1339.644012241219</v>
@@ -17735,7 +17735,7 @@
         </is>
       </c>
       <c r="AG62" s="122" t="n">
-        <v>1284351.763148681</v>
+        <v>1098734.492017637</v>
       </c>
       <c r="AH62" s="56" t="n">
         <v>322.2269528582681</v>
@@ -17763,49 +17763,49 @@
         <v>0</v>
       </c>
       <c r="J63" s="130" t="n">
-        <v>1964.875071784408</v>
+        <v>1964.875071784398</v>
       </c>
       <c r="K63" s="131" t="n">
-        <v>347.8756485030455</v>
+        <v>347.8756485030435</v>
       </c>
       <c r="L63" s="131" t="n">
-        <v>130.6682137649018</v>
+        <v>130.668213764901</v>
       </c>
       <c r="M63" s="131" t="n">
-        <v>663.932716975576</v>
+        <v>663.9327169755762</v>
       </c>
       <c r="N63" s="132" t="n">
-        <v>3107.351651027931</v>
+        <v>3107.351651027918</v>
       </c>
       <c r="P63" s="130" t="n">
-        <v>2163.155319482375</v>
+        <v>2163.155319482363</v>
       </c>
       <c r="Q63" s="131" t="n">
-        <v>372.0859813343212</v>
+        <v>372.0859813343191</v>
       </c>
       <c r="R63" s="131" t="n">
-        <v>143.0165673943964</v>
+        <v>143.0165673943955</v>
       </c>
       <c r="S63" s="131" t="n">
-        <v>753.6182474419385</v>
+        <v>753.6182474419381</v>
       </c>
       <c r="T63" s="132" t="n">
-        <v>3431.876115653031</v>
+        <v>3431.876115653015</v>
       </c>
       <c r="V63" s="130" t="n">
-        <v>2378.866087308556</v>
+        <v>2378.866087308544</v>
       </c>
       <c r="W63" s="131" t="n">
-        <v>407.7078036315904</v>
+        <v>407.7078036315881</v>
       </c>
       <c r="X63" s="131" t="n">
-        <v>157.7761316534636</v>
+        <v>157.7761316534625</v>
       </c>
       <c r="Y63" s="131" t="n">
-        <v>854.1693686244979</v>
+        <v>854.1693686244977</v>
       </c>
       <c r="Z63" s="132" t="n">
-        <v>3798.519391218108</v>
+        <v>3798.519391218092</v>
       </c>
       <c r="AE63" s="121" t="n">
         <v>15</v>
@@ -17816,7 +17816,7 @@
         </is>
       </c>
       <c r="AG63" s="122" t="n">
-        <v>984067.5094943271</v>
+        <v>855527.6690948717</v>
       </c>
       <c r="AH63" s="56" t="n">
         <v>4782.311376407688</v>
@@ -17897,7 +17897,7 @@
         </is>
       </c>
       <c r="AG64" s="122" t="n">
-        <v>884256.2432951636</v>
+        <v>768753.8460624892</v>
       </c>
       <c r="AH64" s="56" t="n">
         <v>2379.392482130931</v>
@@ -17983,7 +17983,7 @@
         </is>
       </c>
       <c r="AG65" s="122" t="n">
-        <v>793722.7915681324</v>
+        <v>690045.960491772</v>
       </c>
       <c r="AH65" s="56" t="n">
         <v>2416.402904257768</v>
@@ -18065,7 +18065,7 @@
         </is>
       </c>
       <c r="AG66" s="122" t="n">
-        <v>789302.3964713198</v>
+        <v>686202.9616353238</v>
       </c>
       <c r="AH66" s="56" t="n">
         <v>555.2245665248699</v>
@@ -18146,7 +18146,7 @@
         </is>
       </c>
       <c r="AG67" s="122" t="n">
-        <v>470417.6769428896</v>
+        <v>408971.2695247711</v>
       </c>
       <c r="AH67" s="56" t="n">
         <v>456.9365505583999</v>
@@ -18174,49 +18174,49 @@
         <v>0</v>
       </c>
       <c r="J68" s="142" t="n">
-        <v>1964.875071784408</v>
+        <v>1964.875071784398</v>
       </c>
       <c r="K68" s="143" t="n">
-        <v>347.8756485030455</v>
+        <v>347.8756485030435</v>
       </c>
       <c r="L68" s="143" t="n">
-        <v>130.6682137649018</v>
+        <v>130.668213764901</v>
       </c>
       <c r="M68" s="143" t="n">
-        <v>663.932716975576</v>
+        <v>663.9327169755762</v>
       </c>
       <c r="N68" s="144" t="n">
-        <v>3107.351651027931</v>
+        <v>3107.351651027918</v>
       </c>
       <c r="P68" s="142" t="n">
-        <v>2163.155319482375</v>
+        <v>2163.155319482363</v>
       </c>
       <c r="Q68" s="143" t="n">
-        <v>372.0859813343212</v>
+        <v>372.0859813343191</v>
       </c>
       <c r="R68" s="143" t="n">
-        <v>143.0165673943964</v>
+        <v>143.0165673943955</v>
       </c>
       <c r="S68" s="143" t="n">
-        <v>753.6182474419385</v>
+        <v>753.6182474419381</v>
       </c>
       <c r="T68" s="144" t="n">
-        <v>3431.876115653031</v>
+        <v>3431.876115653015</v>
       </c>
       <c r="V68" s="142" t="n">
-        <v>2378.866087308556</v>
+        <v>2378.866087308544</v>
       </c>
       <c r="W68" s="143" t="n">
-        <v>407.7078036315904</v>
+        <v>407.7078036315881</v>
       </c>
       <c r="X68" s="143" t="n">
-        <v>157.7761316534636</v>
+        <v>157.7761316534625</v>
       </c>
       <c r="Y68" s="143" t="n">
-        <v>854.1693686244979</v>
+        <v>854.1693686244977</v>
       </c>
       <c r="Z68" s="144" t="n">
-        <v>3798.519391218108</v>
+        <v>3798.519391218092</v>
       </c>
       <c r="AE68" s="124" t="n">
         <v>20</v>
@@ -18227,7 +18227,7 @@
         </is>
       </c>
       <c r="AG68" s="125" t="n">
-        <v>470146.5139239511</v>
+        <v>408735.5260790228</v>
       </c>
       <c r="AH68" s="84" t="n">
         <v>3769.549013211484</v>
@@ -20259,49 +20259,49 @@
         <v>0</v>
       </c>
       <c r="J99" s="130" t="n">
-        <v>1964.875071784408</v>
+        <v>1964.875071784398</v>
       </c>
       <c r="K99" s="131" t="n">
-        <v>347.8756485030455</v>
+        <v>347.8756485030435</v>
       </c>
       <c r="L99" s="131" t="n">
-        <v>130.6682137649018</v>
+        <v>130.668213764901</v>
       </c>
       <c r="M99" s="131" t="n">
-        <v>663.932716975576</v>
+        <v>663.9327169755762</v>
       </c>
       <c r="N99" s="132" t="n">
-        <v>3107.351651027931</v>
+        <v>3107.351651027918</v>
       </c>
       <c r="P99" s="130" t="n">
-        <v>2163.155319482375</v>
+        <v>2163.155319482363</v>
       </c>
       <c r="Q99" s="131" t="n">
-        <v>372.0859813343212</v>
+        <v>372.0859813343191</v>
       </c>
       <c r="R99" s="131" t="n">
-        <v>143.0165673943964</v>
+        <v>143.0165673943955</v>
       </c>
       <c r="S99" s="131" t="n">
-        <v>753.6182474419385</v>
+        <v>753.6182474419381</v>
       </c>
       <c r="T99" s="132" t="n">
-        <v>3431.876115653031</v>
+        <v>3431.876115653015</v>
       </c>
       <c r="V99" s="130" t="n">
-        <v>2378.866087308556</v>
+        <v>2378.866087308544</v>
       </c>
       <c r="W99" s="131" t="n">
-        <v>407.7078036315904</v>
+        <v>407.7078036315881</v>
       </c>
       <c r="X99" s="131" t="n">
-        <v>157.7761316534636</v>
+        <v>157.7761316534625</v>
       </c>
       <c r="Y99" s="131" t="n">
-        <v>854.1693686244979</v>
+        <v>854.1693686244977</v>
       </c>
       <c r="Z99" s="132" t="n">
-        <v>3798.519391218108</v>
+        <v>3798.519391218092</v>
       </c>
     </row>
     <row r="100">
@@ -20598,49 +20598,49 @@
         <v>0</v>
       </c>
       <c r="J104" s="142" t="n">
-        <v>1964.875071784408</v>
+        <v>1964.875071784398</v>
       </c>
       <c r="K104" s="143" t="n">
-        <v>347.8756485030455</v>
+        <v>347.8756485030435</v>
       </c>
       <c r="L104" s="143" t="n">
-        <v>130.6682137649018</v>
+        <v>130.668213764901</v>
       </c>
       <c r="M104" s="143" t="n">
-        <v>663.932716975576</v>
+        <v>663.9327169755762</v>
       </c>
       <c r="N104" s="144" t="n">
-        <v>3107.351651027931</v>
+        <v>3107.351651027918</v>
       </c>
       <c r="P104" s="142" t="n">
-        <v>2163.155319482375</v>
+        <v>2163.155319482363</v>
       </c>
       <c r="Q104" s="143" t="n">
-        <v>372.0859813343212</v>
+        <v>372.0859813343191</v>
       </c>
       <c r="R104" s="143" t="n">
-        <v>143.0165673943964</v>
+        <v>143.0165673943955</v>
       </c>
       <c r="S104" s="143" t="n">
-        <v>753.6182474419385</v>
+        <v>753.6182474419381</v>
       </c>
       <c r="T104" s="144" t="n">
-        <v>3431.876115653031</v>
+        <v>3431.876115653015</v>
       </c>
       <c r="V104" s="142" t="n">
-        <v>2378.866087308556</v>
+        <v>2378.866087308544</v>
       </c>
       <c r="W104" s="143" t="n">
-        <v>407.7078036315904</v>
+        <v>407.7078036315881</v>
       </c>
       <c r="X104" s="143" t="n">
-        <v>157.7761316534636</v>
+        <v>157.7761316534625</v>
       </c>
       <c r="Y104" s="143" t="n">
-        <v>854.1693686244979</v>
+        <v>854.1693686244977</v>
       </c>
       <c r="Z104" s="144" t="n">
-        <v>3798.519391218108</v>
+        <v>3798.519391218092</v>
       </c>
     </row>
     <row r="105" ht="30.3" customHeight="1" thickBot="1"/>
@@ -20651,7 +20651,7 @@
         </is>
       </c>
       <c r="H106" s="111" t="n">
-        <v>-1576682</v>
+        <v>0</v>
       </c>
     </row>
     <row r="107" ht="15" customHeight="1" thickBot="1"/>
@@ -20662,7 +20662,7 @@
         </is>
       </c>
       <c r="H108" s="113" t="n">
-        <v>0</v>
+        <v>1576682</v>
       </c>
     </row>
     <row r="109"/>
@@ -21673,7 +21673,7 @@
         </is>
       </c>
       <c r="AH25" s="119" t="n">
-        <v>55708633.42960343</v>
+        <v>48231122.17847329</v>
       </c>
       <c r="AI25" s="46" t="n">
         <v>68660.90964512639</v>
@@ -21750,7 +21750,7 @@
         </is>
       </c>
       <c r="AH26" s="122" t="n">
-        <v>24728108.06662748</v>
+        <v>21060282.25210969</v>
       </c>
       <c r="AI26" s="56" t="n">
         <v>1727.330050412035</v>
@@ -21827,7 +21827,7 @@
         </is>
       </c>
       <c r="AH27" s="122" t="n">
-        <v>15529300.68992915</v>
+        <v>13225898.83652163</v>
       </c>
       <c r="AI27" s="56" t="n">
         <v>964.0204682757309</v>
@@ -21904,7 +21904,7 @@
         </is>
       </c>
       <c r="AH28" s="122" t="n">
-        <v>13031677.99235527</v>
+        <v>11098738.97340335</v>
       </c>
       <c r="AI28" s="56" t="n">
         <v>6257.992427689866</v>
@@ -21981,7 +21981,7 @@
         </is>
       </c>
       <c r="AH29" s="122" t="n">
-        <v>11517463.76894341</v>
+        <v>9809122.361841764</v>
       </c>
       <c r="AI29" s="56" t="n">
         <v>1286.37431571178</v>
@@ -22058,7 +22058,7 @@
         </is>
       </c>
       <c r="AH30" s="122" t="n">
-        <v>11120746.30711649</v>
+        <v>9628060.155740913</v>
       </c>
       <c r="AI30" s="56" t="n">
         <v>13115.76309006336</v>
@@ -22121,7 +22121,7 @@
         </is>
       </c>
       <c r="AH31" s="122" t="n">
-        <v>10820699.59576299</v>
+        <v>9215706.557009479</v>
       </c>
       <c r="AI31" s="56" t="n">
         <v>518.5073114282314</v>
@@ -22192,7 +22192,7 @@
         </is>
       </c>
       <c r="AH32" s="122" t="n">
-        <v>9352525.180961719</v>
+        <v>7965300.845107484</v>
       </c>
       <c r="AI32" s="56" t="n">
         <v>697.3417203590096</v>
@@ -22269,7 +22269,7 @@
         </is>
       </c>
       <c r="AH33" s="122" t="n">
-        <v>5249960.052605658</v>
+        <v>4545282.286439494</v>
       </c>
       <c r="AI33" s="56" t="n">
         <v>17635.78868488065</v>
@@ -22346,7 +22346,7 @@
         </is>
       </c>
       <c r="AH34" s="122" t="n">
-        <v>4195866.191525102</v>
+        <v>3573509.386464555</v>
       </c>
       <c r="AI34" s="56" t="n">
         <v>510.6340984564362</v>
@@ -22423,7 +22423,7 @@
         </is>
       </c>
       <c r="AH35" s="122" t="n">
-        <v>4094286.127687376</v>
+        <v>3544729.107520738</v>
       </c>
       <c r="AI35" s="56" t="n">
         <v>3709.279945752466</v>
@@ -22500,7 +22500,7 @@
         </is>
       </c>
       <c r="AH36" s="122" t="n">
-        <v>3649660.287984257</v>
+        <v>3159783.330210902</v>
       </c>
       <c r="AI36" s="56" t="n">
         <v>11271.648789632</v>
@@ -22577,7 +22577,7 @@
         </is>
       </c>
       <c r="AH37" s="122" t="n">
-        <v>3508347.829385333</v>
+        <v>2987967.996837878</v>
       </c>
       <c r="AI37" s="56" t="n">
         <v>363.2925414128391</v>
@@ -22654,7 +22654,7 @@
         </is>
       </c>
       <c r="AH38" s="122" t="n">
-        <v>3310332.381333624</v>
+        <v>2866001.833220612</v>
       </c>
       <c r="AI38" s="56" t="n">
         <v>6744.893823437549</v>
@@ -22717,7 +22717,7 @@
         </is>
       </c>
       <c r="AH39" s="122" t="n">
-        <v>2917567.158940644</v>
+        <v>2525955.663309997</v>
       </c>
       <c r="AI39" s="56" t="n">
         <v>2574.249362596877</v>
@@ -22784,7 +22784,7 @@
         </is>
       </c>
       <c r="AH40" s="122" t="n">
-        <v>2640708.444798406</v>
+        <v>2286258.409116118</v>
       </c>
       <c r="AI40" s="56" t="n">
         <v>379.795065741434</v>
@@ -22861,7 +22861,7 @@
         </is>
       </c>
       <c r="AH41" s="122" t="n">
-        <v>2325375.35539304</v>
+        <v>1980461.311262639</v>
       </c>
       <c r="AI41" s="56" t="n">
         <v>404.9080956923283</v>
@@ -22938,7 +22938,7 @@
         </is>
       </c>
       <c r="AH42" s="122" t="n">
-        <v>2071650.330387406</v>
+        <v>1764370.350051832</v>
       </c>
       <c r="AI42" s="56" t="n">
         <v>4658.580961426271</v>
@@ -23015,7 +23015,7 @@
         </is>
       </c>
       <c r="AH43" s="122" t="n">
-        <v>2006758.971569033</v>
+        <v>1737401.030718165</v>
       </c>
       <c r="AI43" s="56" t="n">
         <v>3570.123843302602</v>
@@ -23092,7 +23092,7 @@
         </is>
       </c>
       <c r="AH44" s="125" t="n">
-        <v>1951341.934311199</v>
+        <v>1689422.365110991</v>
       </c>
       <c r="AI44" s="84" t="n">
         <v>2751.314133569148</v>
@@ -23266,7 +23266,7 @@
         </is>
       </c>
       <c r="AG49" s="119" t="n">
-        <v>85612658.37447587</v>
+        <v>72914059.77609868</v>
       </c>
       <c r="AH49" s="46" t="n">
         <v>7828.257255851084</v>
@@ -23282,7 +23282,7 @@
         </is>
       </c>
       <c r="AG50" s="122" t="n">
-        <v>69766048.18223651</v>
+        <v>60401675.40707625</v>
       </c>
       <c r="AH50" s="56" t="n">
         <v>85020.26893827226</v>
@@ -23328,7 +23328,7 @@
         </is>
       </c>
       <c r="AG51" s="122" t="n">
-        <v>15063022.22935024</v>
+        <v>12833999.9192036</v>
       </c>
       <c r="AH51" s="56" t="n">
         <v>7017.358741446604</v>
@@ -23449,7 +23449,7 @@
         </is>
       </c>
       <c r="AG52" s="122" t="n">
-        <v>11277283.09985187</v>
+        <v>9763585.741472377</v>
       </c>
       <c r="AH52" s="56" t="n">
         <v>13739.45626015745</v>
@@ -23530,7 +23530,7 @@
         </is>
       </c>
       <c r="AG53" s="122" t="n">
-        <v>5668064.076149372</v>
+        <v>4907266.147851759</v>
       </c>
       <c r="AH53" s="56" t="n">
         <v>19394.37404755965</v>
@@ -23611,7 +23611,7 @@
         </is>
       </c>
       <c r="AG54" s="122" t="n">
-        <v>5250658.344032554</v>
+        <v>4545886.849449811</v>
       </c>
       <c r="AH54" s="56" t="n">
         <v>24631.48045419634</v>
@@ -23692,7 +23692,7 @@
         </is>
       </c>
       <c r="AG55" s="122" t="n">
-        <v>4099313.275818895</v>
+        <v>3549081.484895906</v>
       </c>
       <c r="AH55" s="56" t="n">
         <v>9509.717978483148</v>
@@ -23773,7 +23773,7 @@
         </is>
       </c>
       <c r="AG56" s="122" t="n">
-        <v>3982941.913335151</v>
+        <v>3448330.11017189</v>
       </c>
       <c r="AH56" s="56" t="n">
         <v>12535.421478272</v>
@@ -23854,7 +23854,7 @@
         </is>
       </c>
       <c r="AG57" s="122" t="n">
-        <v>3002169.169474884</v>
+        <v>2599201.938715006</v>
       </c>
       <c r="AH57" s="56" t="n">
         <v>746.4683132581457</v>
@@ -23935,7 +23935,7 @@
         </is>
       </c>
       <c r="AG58" s="122" t="n">
-        <v>2311210.540960126</v>
+        <v>1968397.509648616</v>
       </c>
       <c r="AH58" s="56" t="n">
         <v>1913.62175231616</v>
@@ -24016,7 +24016,7 @@
         </is>
       </c>
       <c r="AG59" s="122" t="n">
-        <v>2149531.545200148</v>
+        <v>1830699.741757585</v>
       </c>
       <c r="AH59" s="56" t="n">
         <v>5120.548802068751</v>
@@ -24097,7 +24097,7 @@
         </is>
       </c>
       <c r="AG60" s="122" t="n">
-        <v>1788780.905197965</v>
+        <v>1523457.866212379</v>
       </c>
       <c r="AH60" s="56" t="n">
         <v>439.2059294319066</v>
@@ -24178,7 +24178,7 @@
         </is>
       </c>
       <c r="AG61" s="122" t="n">
-        <v>1317225.392525605</v>
+        <v>1121852.657889074</v>
       </c>
       <c r="AH61" s="56" t="n">
         <v>1356.093560047119</v>
@@ -24259,7 +24259,7 @@
         </is>
       </c>
       <c r="AG62" s="122" t="n">
-        <v>1281195.799837103</v>
+        <v>1091160.920685299</v>
       </c>
       <c r="AH62" s="56" t="n">
         <v>303.3444534207736</v>
@@ -24287,49 +24287,49 @@
         <v>0</v>
       </c>
       <c r="J63" s="130" t="n">
-        <v>1964.875071784408</v>
+        <v>1964.875071784398</v>
       </c>
       <c r="K63" s="131" t="n">
-        <v>347.8756485030455</v>
+        <v>347.8756485030435</v>
       </c>
       <c r="L63" s="131" t="n">
-        <v>130.6682137649018</v>
+        <v>130.668213764901</v>
       </c>
       <c r="M63" s="131" t="n">
-        <v>663.932716975576</v>
+        <v>663.9327169755762</v>
       </c>
       <c r="N63" s="132" t="n">
-        <v>3107.351651027931</v>
+        <v>3107.351651027918</v>
       </c>
       <c r="P63" s="130" t="n">
-        <v>2163.155319482375</v>
+        <v>2163.155319482363</v>
       </c>
       <c r="Q63" s="131" t="n">
-        <v>372.0859813343212</v>
+        <v>372.0859813343191</v>
       </c>
       <c r="R63" s="131" t="n">
-        <v>143.0165673943964</v>
+        <v>143.0165673943955</v>
       </c>
       <c r="S63" s="131" t="n">
-        <v>753.6182474419385</v>
+        <v>753.6182474419381</v>
       </c>
       <c r="T63" s="132" t="n">
-        <v>3431.876115653031</v>
+        <v>3431.876115653015</v>
       </c>
       <c r="V63" s="130" t="n">
-        <v>2378.866087308556</v>
+        <v>2378.866087308544</v>
       </c>
       <c r="W63" s="131" t="n">
-        <v>407.7078036315904</v>
+        <v>407.7078036315881</v>
       </c>
       <c r="X63" s="131" t="n">
-        <v>157.7761316534636</v>
+        <v>157.7761316534625</v>
       </c>
       <c r="Y63" s="131" t="n">
-        <v>854.1693686244979</v>
+        <v>854.1693686244977</v>
       </c>
       <c r="Z63" s="132" t="n">
-        <v>3798.519391218108</v>
+        <v>3798.519391218092</v>
       </c>
       <c r="AE63" s="121" t="n">
         <v>15</v>
@@ -24340,7 +24340,7 @@
         </is>
       </c>
       <c r="AG63" s="122" t="n">
-        <v>978732.3346700597</v>
+        <v>847361.6369201627</v>
       </c>
       <c r="AH63" s="56" t="n">
         <v>4559.025258243213</v>
@@ -24421,7 +24421,7 @@
         </is>
       </c>
       <c r="AG64" s="122" t="n">
-        <v>852544.2733268536</v>
+        <v>738111.2132528919</v>
       </c>
       <c r="AH64" s="56" t="n">
         <v>572.0217893287144</v>
@@ -24507,7 +24507,7 @@
         </is>
       </c>
       <c r="AG65" s="122" t="n">
-        <v>769221.9314309077</v>
+        <v>665972.8425054173</v>
       </c>
       <c r="AH65" s="56" t="n">
         <v>2303.581052657972</v>
@@ -24589,7 +24589,7 @@
         </is>
       </c>
       <c r="AG66" s="122" t="n">
-        <v>584794.7540085486</v>
+        <v>506300.4689490068</v>
       </c>
       <c r="AH66" s="56" t="n">
         <v>539.185129658912</v>
@@ -24670,7 +24670,7 @@
         </is>
       </c>
       <c r="AG67" s="122" t="n">
-        <v>518402.8556809945</v>
+        <v>448820.0469253099</v>
       </c>
       <c r="AH67" s="56" t="n">
         <v>3956.458053460796</v>
@@ -24698,49 +24698,49 @@
         <v>0</v>
       </c>
       <c r="J68" s="142" t="n">
-        <v>1964.875071784408</v>
+        <v>1964.875071784398</v>
       </c>
       <c r="K68" s="143" t="n">
-        <v>347.8756485030455</v>
+        <v>347.8756485030435</v>
       </c>
       <c r="L68" s="143" t="n">
-        <v>130.6682137649018</v>
+        <v>130.668213764901</v>
       </c>
       <c r="M68" s="143" t="n">
-        <v>663.932716975576</v>
+        <v>663.9327169755762</v>
       </c>
       <c r="N68" s="144" t="n">
-        <v>3107.351651027931</v>
+        <v>3107.351651027918</v>
       </c>
       <c r="P68" s="142" t="n">
-        <v>2163.155319482375</v>
+        <v>2163.155319482363</v>
       </c>
       <c r="Q68" s="143" t="n">
-        <v>372.0859813343212</v>
+        <v>372.0859813343191</v>
       </c>
       <c r="R68" s="143" t="n">
-        <v>143.0165673943964</v>
+        <v>143.0165673943955</v>
       </c>
       <c r="S68" s="143" t="n">
-        <v>753.6182474419385</v>
+        <v>753.6182474419381</v>
       </c>
       <c r="T68" s="144" t="n">
-        <v>3431.876115653031</v>
+        <v>3431.876115653015</v>
       </c>
       <c r="V68" s="142" t="n">
-        <v>2378.866087308556</v>
+        <v>2378.866087308544</v>
       </c>
       <c r="W68" s="143" t="n">
-        <v>407.7078036315904</v>
+        <v>407.7078036315881</v>
       </c>
       <c r="X68" s="143" t="n">
-        <v>157.7761316534636</v>
+        <v>157.7761316534625</v>
       </c>
       <c r="Y68" s="143" t="n">
-        <v>854.1693686244979</v>
+        <v>854.1693686244977</v>
       </c>
       <c r="Z68" s="144" t="n">
-        <v>3798.519391218108</v>
+        <v>3798.519391218092</v>
       </c>
       <c r="AE68" s="124" t="n">
         <v>20</v>
@@ -24751,7 +24751,7 @@
         </is>
       </c>
       <c r="AG68" s="125" t="n">
-        <v>442089.1120680772</v>
+        <v>376515.7227415848</v>
       </c>
       <c r="AH68" s="84" t="n">
         <v>234.9247334314719</v>
@@ -26783,49 +26783,49 @@
         <v>0</v>
       </c>
       <c r="J99" s="130" t="n">
-        <v>1964.875071784408</v>
+        <v>1964.875071784398</v>
       </c>
       <c r="K99" s="131" t="n">
-        <v>347.8756485030455</v>
+        <v>347.8756485030435</v>
       </c>
       <c r="L99" s="131" t="n">
-        <v>130.6682137649018</v>
+        <v>130.668213764901</v>
       </c>
       <c r="M99" s="131" t="n">
-        <v>663.932716975576</v>
+        <v>663.9327169755762</v>
       </c>
       <c r="N99" s="132" t="n">
-        <v>3107.351651027931</v>
+        <v>3107.351651027918</v>
       </c>
       <c r="P99" s="130" t="n">
-        <v>2163.155319482375</v>
+        <v>2163.155319482363</v>
       </c>
       <c r="Q99" s="131" t="n">
-        <v>372.0859813343212</v>
+        <v>372.0859813343191</v>
       </c>
       <c r="R99" s="131" t="n">
-        <v>143.0165673943964</v>
+        <v>143.0165673943955</v>
       </c>
       <c r="S99" s="131" t="n">
-        <v>753.6182474419385</v>
+        <v>753.6182474419381</v>
       </c>
       <c r="T99" s="132" t="n">
-        <v>3431.876115653031</v>
+        <v>3431.876115653015</v>
       </c>
       <c r="V99" s="130" t="n">
-        <v>2378.866087308556</v>
+        <v>2378.866087308544</v>
       </c>
       <c r="W99" s="131" t="n">
-        <v>407.7078036315904</v>
+        <v>407.7078036315881</v>
       </c>
       <c r="X99" s="131" t="n">
-        <v>157.7761316534636</v>
+        <v>157.7761316534625</v>
       </c>
       <c r="Y99" s="131" t="n">
-        <v>854.1693686244979</v>
+        <v>854.1693686244977</v>
       </c>
       <c r="Z99" s="132" t="n">
-        <v>3798.519391218108</v>
+        <v>3798.519391218092</v>
       </c>
     </row>
     <row r="100">
@@ -27122,49 +27122,49 @@
         <v>0</v>
       </c>
       <c r="J104" s="142" t="n">
-        <v>1964.875071784408</v>
+        <v>1964.875071784398</v>
       </c>
       <c r="K104" s="143" t="n">
-        <v>347.8756485030455</v>
+        <v>347.8756485030435</v>
       </c>
       <c r="L104" s="143" t="n">
-        <v>130.6682137649018</v>
+        <v>130.668213764901</v>
       </c>
       <c r="M104" s="143" t="n">
-        <v>663.932716975576</v>
+        <v>663.9327169755762</v>
       </c>
       <c r="N104" s="144" t="n">
-        <v>3107.351651027931</v>
+        <v>3107.351651027918</v>
       </c>
       <c r="P104" s="142" t="n">
-        <v>2163.155319482375</v>
+        <v>2163.155319482363</v>
       </c>
       <c r="Q104" s="143" t="n">
-        <v>372.0859813343212</v>
+        <v>372.0859813343191</v>
       </c>
       <c r="R104" s="143" t="n">
-        <v>143.0165673943964</v>
+        <v>143.0165673943955</v>
       </c>
       <c r="S104" s="143" t="n">
-        <v>753.6182474419385</v>
+        <v>753.6182474419381</v>
       </c>
       <c r="T104" s="144" t="n">
-        <v>3431.876115653031</v>
+        <v>3431.876115653015</v>
       </c>
       <c r="V104" s="142" t="n">
-        <v>2378.866087308556</v>
+        <v>2378.866087308544</v>
       </c>
       <c r="W104" s="143" t="n">
-        <v>407.7078036315904</v>
+        <v>407.7078036315881</v>
       </c>
       <c r="X104" s="143" t="n">
-        <v>157.7761316534636</v>
+        <v>157.7761316534625</v>
       </c>
       <c r="Y104" s="143" t="n">
-        <v>854.1693686244979</v>
+        <v>854.1693686244977</v>
       </c>
       <c r="Z104" s="144" t="n">
-        <v>3798.519391218108</v>
+        <v>3798.519391218092</v>
       </c>
     </row>
     <row r="105" ht="30.3" customHeight="1" thickBot="1"/>
@@ -27175,7 +27175,7 @@
         </is>
       </c>
       <c r="H106" s="111" t="n">
-        <v>-1576682</v>
+        <v>0</v>
       </c>
     </row>
     <row r="107" ht="15" customHeight="1" thickBot="1"/>
@@ -27186,7 +27186,7 @@
         </is>
       </c>
       <c r="H108" s="113" t="n">
-        <v>0</v>
+        <v>1576682</v>
       </c>
     </row>
     <row r="109"/>
@@ -28197,7 +28197,7 @@
         </is>
       </c>
       <c r="AH25" s="119" t="n">
-        <v>69272501.28316739</v>
+        <v>60065516.51359829</v>
       </c>
       <c r="AI25" s="46" t="n">
         <v>82393.09157415167</v>
@@ -28274,7 +28274,7 @@
         </is>
       </c>
       <c r="AH26" s="122" t="n">
-        <v>30879003.96205981</v>
+        <v>26334672.11082928</v>
       </c>
       <c r="AI26" s="56" t="n">
         <v>2045.210599589361</v>
@@ -28351,7 +28351,7 @@
         </is>
       </c>
       <c r="AH27" s="122" t="n">
-        <v>19863574.56683606</v>
+        <v>16940336.67048831</v>
       </c>
       <c r="AI27" s="56" t="n">
         <v>1141.429155052513</v>
@@ -28428,7 +28428,7 @@
         </is>
       </c>
       <c r="AH28" s="122" t="n">
-        <v>16598675.10338615</v>
+        <v>14155918.5930653</v>
       </c>
       <c r="AI28" s="56" t="n">
         <v>7591.883513651961</v>
@@ -28505,7 +28505,7 @@
         </is>
       </c>
       <c r="AH29" s="122" t="n">
-        <v>14570481.40100322</v>
+        <v>12426205.5428928</v>
       </c>
       <c r="AI29" s="56" t="n">
         <v>1523.105781032218</v>
@@ -28582,7 +28582,7 @@
         </is>
       </c>
       <c r="AH30" s="122" t="n">
-        <v>11245700.87172256</v>
+        <v>9590718.84174614</v>
       </c>
       <c r="AI30" s="56" t="n">
         <v>528.8307919987675</v>
@@ -28645,7 +28645,7 @@
         </is>
       </c>
       <c r="AH31" s="122" t="n">
-        <v>11231894.20896714</v>
+        <v>9739066.939851334</v>
       </c>
       <c r="AI31" s="56" t="n">
         <v>12591.13256646082</v>
@@ -28716,7 +28716,7 @@
         </is>
       </c>
       <c r="AH32" s="122" t="n">
-        <v>9719861.423889039</v>
+        <v>8289430.704284329</v>
       </c>
       <c r="AI32" s="56" t="n">
         <v>711.2257940113578</v>
@@ -28793,7 +28793,7 @@
         </is>
       </c>
       <c r="AH33" s="122" t="n">
-        <v>6042412.593942057</v>
+        <v>5239317.575090829</v>
       </c>
       <c r="AI33" s="56" t="n">
         <v>19785.76768345444</v>
@@ -28870,7 +28870,7 @@
         </is>
       </c>
       <c r="AH34" s="122" t="n">
-        <v>5241847.482288072</v>
+        <v>4545155.302276412</v>
       </c>
       <c r="AI34" s="56" t="n">
         <v>15780.30830548479</v>
@@ -28947,7 +28947,7 @@
         </is>
       </c>
       <c r="AH35" s="122" t="n">
-        <v>4646252.15196317</v>
+        <v>4028720.346321596</v>
       </c>
       <c r="AI35" s="56" t="n">
         <v>3983.989218534894</v>
@@ -29024,7 +29024,7 @@
         </is>
       </c>
       <c r="AH36" s="122" t="n">
-        <v>4551154.37811714</v>
+        <v>3881380.31980372</v>
       </c>
       <c r="AI36" s="56" t="n">
         <v>520.800823356704</v>
@@ -29101,7 +29101,7 @@
         </is>
       </c>
       <c r="AH37" s="122" t="n">
-        <v>3804988.392237822</v>
+        <v>3245024.412646579</v>
       </c>
       <c r="AI37" s="56" t="n">
         <v>370.5256959123686</v>
@@ -29178,7 +29178,7 @@
         </is>
       </c>
       <c r="AH38" s="122" t="n">
-        <v>3553933.411633193</v>
+        <v>3081581.321166373</v>
       </c>
       <c r="AI38" s="56" t="n">
         <v>6912.032292382333</v>
@@ -29241,7 +29241,7 @@
         </is>
       </c>
       <c r="AH39" s="122" t="n">
-        <v>3344521.812389606</v>
+        <v>2900002.546912395</v>
       </c>
       <c r="AI39" s="56" t="n">
         <v>2764.898270390802</v>
@@ -29308,7 +29308,7 @@
         </is>
       </c>
       <c r="AH40" s="122" t="n">
-        <v>3093025.002358095</v>
+        <v>2681932.093034679</v>
       </c>
       <c r="AI40" s="56" t="n">
         <v>413.2284253786525</v>
@@ -29385,7 +29385,7 @@
         </is>
       </c>
       <c r="AH41" s="122" t="n">
-        <v>2541300.668974575</v>
+        <v>2167308.243967474</v>
       </c>
       <c r="AI41" s="56" t="n">
         <v>5497.125534483</v>
@@ -29462,7 +29462,7 @@
         </is>
       </c>
       <c r="AH42" s="122" t="n">
-        <v>2478636.557893779</v>
+        <v>2113866.143941937</v>
       </c>
       <c r="AI42" s="56" t="n">
         <v>412.9698158775626</v>
@@ -29539,7 +29539,7 @@
         </is>
       </c>
       <c r="AH43" s="122" t="n">
-        <v>2258685.990072574</v>
+        <v>1958484.797324674</v>
       </c>
       <c r="AI43" s="56" t="n">
         <v>2955.076458301281</v>
@@ -29616,7 +29616,7 @@
         </is>
       </c>
       <c r="AH44" s="125" t="n">
-        <v>1704241.930239131</v>
+        <v>1477731.710386777</v>
       </c>
       <c r="AI44" s="84" t="n">
         <v>1964.64427492442</v>
@@ -29790,7 +29790,7 @@
         </is>
       </c>
       <c r="AG49" s="119" t="n">
-        <v>100998472.6616614</v>
+        <v>86134956.44183944</v>
       </c>
       <c r="AH49" s="46" t="n">
         <v>8635.831326759606</v>
@@ -29806,7 +29806,7 @@
         </is>
       </c>
       <c r="AG50" s="122" t="n">
-        <v>83433807.47507648</v>
+        <v>72344648.27826762</v>
       </c>
       <c r="AH50" s="56" t="n">
         <v>98089.91226472027</v>
@@ -29852,7 +29852,7 @@
         </is>
       </c>
       <c r="AG51" s="122" t="n">
-        <v>18794436.51910122</v>
+        <v>16034106.61405382</v>
       </c>
       <c r="AH51" s="56" t="n">
         <v>8347.94335138749</v>
@@ -29973,7 +29973,7 @@
         </is>
       </c>
       <c r="AG52" s="122" t="n">
-        <v>12891459.36337956</v>
+        <v>11178059.84961037</v>
       </c>
       <c r="AH52" s="56" t="n">
         <v>14707.25774155487</v>
@@ -30054,7 +30054,7 @@
         </is>
       </c>
       <c r="AG53" s="122" t="n">
-        <v>6523627.115981039</v>
+        <v>5656574.037391249</v>
       </c>
       <c r="AH53" s="56" t="n">
         <v>21752.76905119918</v>
@@ -30135,7 +30135,7 @@
         </is>
       </c>
       <c r="AG54" s="122" t="n">
-        <v>5734707.282319224</v>
+        <v>4972509.272600757</v>
       </c>
       <c r="AH54" s="56" t="n">
         <v>17549.59006958079</v>
@@ -30216,7 +30216,7 @@
         </is>
       </c>
       <c r="AG55" s="122" t="n">
-        <v>5595708.876836259</v>
+        <v>4851985.09828558</v>
       </c>
       <c r="AH55" s="56" t="n">
         <v>25241.84853985133</v>
@@ -30297,7 +30297,7 @@
         </is>
       </c>
       <c r="AG56" s="122" t="n">
-        <v>3500805.438701428</v>
+        <v>3035514.569188957</v>
       </c>
       <c r="AH56" s="56" t="n">
         <v>772.8172375441062</v>
@@ -30378,7 +30378,7 @@
         </is>
       </c>
       <c r="AG57" s="122" t="n">
-        <v>3250556.563677159</v>
+        <v>2818526.187697785</v>
       </c>
       <c r="AH57" s="56" t="n">
         <v>7784.134951291771</v>
@@ -30459,7 +30459,7 @@
         </is>
       </c>
       <c r="AG58" s="122" t="n">
-        <v>2696810.966029203</v>
+        <v>2299932.751151162</v>
       </c>
       <c r="AH58" s="56" t="n">
         <v>2135.793237760066</v>
@@ -30540,7 +30540,7 @@
         </is>
       </c>
       <c r="AG59" s="122" t="n">
-        <v>2639799.608883559</v>
+        <v>2251311.513274816</v>
       </c>
       <c r="AH59" s="56" t="n">
         <v>6042.247586441125</v>
@@ -30621,7 +30621,7 @@
         </is>
       </c>
       <c r="AG60" s="122" t="n">
-        <v>1891631.383423131</v>
+        <v>1613248.027630991</v>
       </c>
       <c r="AH60" s="56" t="n">
         <v>447.5728023875844</v>
@@ -30702,7 +30702,7 @@
         </is>
       </c>
       <c r="AG61" s="122" t="n">
-        <v>1291690.181123719</v>
+        <v>1101597.62375968</v>
       </c>
       <c r="AH61" s="56" t="n">
         <v>285.5684684503163</v>
@@ -30783,7 +30783,7 @@
         </is>
       </c>
       <c r="AG62" s="122" t="n">
-        <v>1229066.593600664</v>
+        <v>1048196.995950257</v>
       </c>
       <c r="AH62" s="56" t="n">
         <v>1366.252138161891</v>
@@ -30811,49 +30811,49 @@
         <v>0</v>
       </c>
       <c r="J63" s="130" t="n">
-        <v>1964.875071784408</v>
+        <v>1964.875071784398</v>
       </c>
       <c r="K63" s="131" t="n">
-        <v>347.8756485030455</v>
+        <v>347.8756485030435</v>
       </c>
       <c r="L63" s="131" t="n">
-        <v>130.6682137649018</v>
+        <v>130.668213764901</v>
       </c>
       <c r="M63" s="131" t="n">
-        <v>663.932716975576</v>
+        <v>663.9327169755762</v>
       </c>
       <c r="N63" s="132" t="n">
-        <v>3107.351651027931</v>
+        <v>3107.351651027918</v>
       </c>
       <c r="P63" s="130" t="n">
-        <v>2163.155319482375</v>
+        <v>2163.155319482363</v>
       </c>
       <c r="Q63" s="131" t="n">
-        <v>372.0859813343212</v>
+        <v>372.0859813343191</v>
       </c>
       <c r="R63" s="131" t="n">
-        <v>143.0165673943964</v>
+        <v>143.0165673943955</v>
       </c>
       <c r="S63" s="131" t="n">
-        <v>753.6182474419385</v>
+        <v>753.6182474419381</v>
       </c>
       <c r="T63" s="132" t="n">
-        <v>3431.876115653031</v>
+        <v>3431.876115653015</v>
       </c>
       <c r="V63" s="130" t="n">
-        <v>2378.866087308556</v>
+        <v>2378.866087308544</v>
       </c>
       <c r="W63" s="131" t="n">
-        <v>407.7078036315904</v>
+        <v>407.7078036315881</v>
       </c>
       <c r="X63" s="131" t="n">
-        <v>157.7761316534636</v>
+        <v>157.7761316534625</v>
       </c>
       <c r="Y63" s="131" t="n">
-        <v>854.1693686244979</v>
+        <v>854.1693686244977</v>
       </c>
       <c r="Z63" s="132" t="n">
-        <v>3798.519391218108</v>
+        <v>3798.519391218092</v>
       </c>
       <c r="AE63" s="121" t="n">
         <v>15</v>
@@ -30864,7 +30864,7 @@
         </is>
       </c>
       <c r="AG63" s="122" t="n">
-        <v>982714.4737153186</v>
+        <v>852102.2246304051</v>
       </c>
       <c r="AH63" s="56" t="n">
         <v>4346.164368935838</v>
@@ -30945,7 +30945,7 @@
         </is>
       </c>
       <c r="AG64" s="122" t="n">
-        <v>929698.0444135315</v>
+        <v>806132.1910567465</v>
       </c>
       <c r="AH64" s="56" t="n">
         <v>589.389923203073</v>
@@ -31031,7 +31031,7 @@
         </is>
       </c>
       <c r="AG65" s="122" t="n">
-        <v>752557.7618006412</v>
+        <v>652535.5636300209</v>
       </c>
       <c r="AH65" s="56" t="n">
         <v>2196.026853309372</v>
@@ -31113,7 +31113,7 @@
         </is>
       </c>
       <c r="AG66" s="122" t="n">
-        <v>733941.4326166753</v>
+        <v>636393.5244758234</v>
       </c>
       <c r="AH66" s="56" t="n">
         <v>636.2384529975161</v>
@@ -31194,7 +31194,7 @@
         </is>
       </c>
       <c r="AG67" s="122" t="n">
-        <v>577074.2020220398</v>
+        <v>500375.4645647393</v>
       </c>
       <c r="AH67" s="56" t="n">
         <v>4031.203022795794</v>
@@ -31222,49 +31222,49 @@
         <v>0</v>
       </c>
       <c r="J68" s="142" t="n">
-        <v>1964.875071784408</v>
+        <v>1964.875071784398</v>
       </c>
       <c r="K68" s="143" t="n">
-        <v>347.8756485030455</v>
+        <v>347.8756485030435</v>
       </c>
       <c r="L68" s="143" t="n">
-        <v>130.6682137649018</v>
+        <v>130.668213764901</v>
       </c>
       <c r="M68" s="143" t="n">
-        <v>663.932716975576</v>
+        <v>663.9327169755762</v>
       </c>
       <c r="N68" s="144" t="n">
-        <v>3107.351651027931</v>
+        <v>3107.351651027918</v>
       </c>
       <c r="P68" s="142" t="n">
-        <v>2163.155319482375</v>
+        <v>2163.155319482363</v>
       </c>
       <c r="Q68" s="143" t="n">
-        <v>372.0859813343212</v>
+        <v>372.0859813343191</v>
       </c>
       <c r="R68" s="143" t="n">
-        <v>143.0165673943964</v>
+        <v>143.0165673943955</v>
       </c>
       <c r="S68" s="143" t="n">
-        <v>753.6182474419385</v>
+        <v>753.6182474419381</v>
       </c>
       <c r="T68" s="144" t="n">
-        <v>3431.876115653031</v>
+        <v>3431.876115653015</v>
       </c>
       <c r="V68" s="142" t="n">
-        <v>2378.866087308556</v>
+        <v>2378.866087308544</v>
       </c>
       <c r="W68" s="143" t="n">
-        <v>407.7078036315904</v>
+        <v>407.7078036315881</v>
       </c>
       <c r="X68" s="143" t="n">
-        <v>157.7761316534636</v>
+        <v>157.7761316534625</v>
       </c>
       <c r="Y68" s="143" t="n">
-        <v>854.1693686244979</v>
+        <v>854.1693686244977</v>
       </c>
       <c r="Z68" s="144" t="n">
-        <v>3798.519391218108</v>
+        <v>3798.519391218092</v>
       </c>
       <c r="AE68" s="124" t="n">
         <v>20</v>
@@ -31275,7 +31275,7 @@
         </is>
       </c>
       <c r="AG68" s="125" t="n">
-        <v>522946.3976335505</v>
+        <v>445986.5975644719</v>
       </c>
       <c r="AH68" s="84" t="n">
         <v>262.1994949828659</v>
@@ -33307,49 +33307,49 @@
         <v>0</v>
       </c>
       <c r="J99" s="130" t="n">
-        <v>1964.875071784408</v>
+        <v>1964.875071784398</v>
       </c>
       <c r="K99" s="131" t="n">
-        <v>347.8756485030455</v>
+        <v>347.8756485030435</v>
       </c>
       <c r="L99" s="131" t="n">
-        <v>130.6682137649018</v>
+        <v>130.668213764901</v>
       </c>
       <c r="M99" s="131" t="n">
-        <v>663.932716975576</v>
+        <v>663.9327169755762</v>
       </c>
       <c r="N99" s="132" t="n">
-        <v>3107.351651027931</v>
+        <v>3107.351651027918</v>
       </c>
       <c r="P99" s="130" t="n">
-        <v>2163.155319482375</v>
+        <v>2163.155319482363</v>
       </c>
       <c r="Q99" s="131" t="n">
-        <v>372.0859813343212</v>
+        <v>372.0859813343191</v>
       </c>
       <c r="R99" s="131" t="n">
-        <v>143.0165673943964</v>
+        <v>143.0165673943955</v>
       </c>
       <c r="S99" s="131" t="n">
-        <v>753.6182474419385</v>
+        <v>753.6182474419381</v>
       </c>
       <c r="T99" s="132" t="n">
-        <v>3431.876115653031</v>
+        <v>3431.876115653015</v>
       </c>
       <c r="V99" s="130" t="n">
-        <v>2378.866087308556</v>
+        <v>2378.866087308544</v>
       </c>
       <c r="W99" s="131" t="n">
-        <v>407.7078036315904</v>
+        <v>407.7078036315881</v>
       </c>
       <c r="X99" s="131" t="n">
-        <v>157.7761316534636</v>
+        <v>157.7761316534625</v>
       </c>
       <c r="Y99" s="131" t="n">
-        <v>854.1693686244979</v>
+        <v>854.1693686244977</v>
       </c>
       <c r="Z99" s="132" t="n">
-        <v>3798.519391218108</v>
+        <v>3798.519391218092</v>
       </c>
     </row>
     <row r="100">
@@ -33646,49 +33646,49 @@
         <v>0</v>
       </c>
       <c r="J104" s="142" t="n">
-        <v>1964.875071784408</v>
+        <v>1964.875071784398</v>
       </c>
       <c r="K104" s="143" t="n">
-        <v>347.8756485030455</v>
+        <v>347.8756485030435</v>
       </c>
       <c r="L104" s="143" t="n">
-        <v>130.6682137649018</v>
+        <v>130.668213764901</v>
       </c>
       <c r="M104" s="143" t="n">
-        <v>663.932716975576</v>
+        <v>663.9327169755762</v>
       </c>
       <c r="N104" s="144" t="n">
-        <v>3107.351651027931</v>
+        <v>3107.351651027918</v>
       </c>
       <c r="P104" s="142" t="n">
-        <v>2163.155319482375</v>
+        <v>2163.155319482363</v>
       </c>
       <c r="Q104" s="143" t="n">
-        <v>372.0859813343212</v>
+        <v>372.0859813343191</v>
       </c>
       <c r="R104" s="143" t="n">
-        <v>143.0165673943964</v>
+        <v>143.0165673943955</v>
       </c>
       <c r="S104" s="143" t="n">
-        <v>753.6182474419385</v>
+        <v>753.6182474419381</v>
       </c>
       <c r="T104" s="144" t="n">
-        <v>3431.876115653031</v>
+        <v>3431.876115653015</v>
       </c>
       <c r="V104" s="142" t="n">
-        <v>2378.866087308556</v>
+        <v>2378.866087308544</v>
       </c>
       <c r="W104" s="143" t="n">
-        <v>407.7078036315904</v>
+        <v>407.7078036315881</v>
       </c>
       <c r="X104" s="143" t="n">
-        <v>157.7761316534636</v>
+        <v>157.7761316534625</v>
       </c>
       <c r="Y104" s="143" t="n">
-        <v>854.1693686244979</v>
+        <v>854.1693686244977</v>
       </c>
       <c r="Z104" s="144" t="n">
-        <v>3798.519391218108</v>
+        <v>3798.519391218092</v>
       </c>
     </row>
     <row r="105" ht="30.3" customHeight="1" thickBot="1"/>
@@ -33699,7 +33699,7 @@
         </is>
       </c>
       <c r="H106" s="111" t="n">
-        <v>-1576682</v>
+        <v>0</v>
       </c>
     </row>
     <row r="107" ht="15" customHeight="1" thickBot="1"/>
@@ -33710,7 +33710,7 @@
         </is>
       </c>
       <c r="H108" s="113" t="n">
-        <v>0</v>
+        <v>1576682</v>
       </c>
     </row>
     <row r="109"/>
